--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111332</v>
+        <v>111338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111338</v>
+        <v>111340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98221</v>
+        <v>98223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111340</v>
+        <v>111341</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111341</v>
+        <v>111347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111347</v>
+        <v>111351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111351</v>
+        <v>111353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111353</v>
+        <v>111355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111355</v>
+        <v>111368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111368</v>
+        <v>111370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111370</v>
+        <v>111376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111376</v>
+        <v>111398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111398</v>
+        <v>111399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111399</v>
+        <v>111404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111404</v>
+        <v>111407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111407</v>
+        <v>111413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111413</v>
+        <v>111414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111414</v>
+        <v>111426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79292</v>
+        <v>79293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111430</v>
+        <v>111432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37212-2026 artfynd.xlsx
+++ b/artfynd/A 37212-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136967751</v>
       </c>
       <c r="B2" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136968163</v>
       </c>
       <c r="B3" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136967894</v>
       </c>
       <c r="B4" t="n">
-        <v>79293</v>
+        <v>79296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136967789</v>
       </c>
       <c r="B5" t="n">
-        <v>111432</v>
+        <v>111436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>136967762</v>
       </c>
       <c r="B6" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
